--- a/demo_data/sample_ar_aging.xlsx
+++ b/demo_data/sample_ar_aging.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="59">
   <si>
     <t>Müşteri</t>
   </si>
@@ -31,40 +31,37 @@
     <t>Para Birimi</t>
   </si>
   <si>
+    <t>Sahil Turizm AŞ</t>
+  </si>
+  <si>
+    <t>Marmara İnşaat AŞ</t>
+  </si>
+  <si>
+    <t>Akdeniz Kimya AŞ</t>
+  </si>
+  <si>
+    <t>Boğaz Elektronik</t>
+  </si>
+  <si>
+    <t>Orta Anadolu Tarım</t>
+  </si>
+  <si>
     <t>Anadolu Market Zinciri</t>
   </si>
   <si>
-    <t>Ege Gıda Dağıtım</t>
-  </si>
-  <si>
-    <t>Marmara İnşaat AŞ</t>
-  </si>
-  <si>
-    <t>Karadeniz Tekstil</t>
-  </si>
-  <si>
-    <t>Akdeniz Lojistik</t>
-  </si>
-  <si>
-    <t>Star Elektronik</t>
-  </si>
-  <si>
-    <t>Beta Yapı Malzemeleri</t>
-  </si>
-  <si>
-    <t>Nova Kimya</t>
-  </si>
-  <si>
-    <t>Vega Otomotiv</t>
-  </si>
-  <si>
-    <t>Sun Perakende</t>
+    <t>İç Anadolu Lojistik</t>
+  </si>
+  <si>
+    <t>Karadeniz Gıda Ltd.</t>
+  </si>
+  <si>
+    <t>Güney Yapı Market</t>
   </si>
   <si>
     <t>Delta Mobilya</t>
   </si>
   <si>
-    <t>Orion Ambalaj</t>
+    <t>Ege Tekstil San.</t>
   </si>
   <si>
     <t>FA1000</t>
@@ -97,27 +94,48 @@
     <t>FA1009</t>
   </si>
   <si>
+    <t>FA1010</t>
+  </si>
+  <si>
+    <t>FA1011</t>
+  </si>
+  <si>
     <t>FA1012</t>
   </si>
   <si>
     <t>FA1013</t>
   </si>
   <si>
+    <t>FA1014</t>
+  </si>
+  <si>
     <t>FA1015</t>
   </si>
   <si>
     <t>FA1016</t>
   </si>
   <si>
+    <t>FA1017</t>
+  </si>
+  <si>
     <t>FA1018</t>
   </si>
   <si>
+    <t>FA1019</t>
+  </si>
+  <si>
+    <t>FA1020</t>
+  </si>
+  <si>
     <t>FA1021</t>
   </si>
   <si>
     <t>FA1022</t>
   </si>
   <si>
+    <t>FA1023</t>
+  </si>
+  <si>
     <t>FA1024</t>
   </si>
   <si>
@@ -130,6 +148,12 @@
     <t>FA1027</t>
   </si>
   <si>
+    <t>FA1028</t>
+  </si>
+  <si>
+    <t>FA1029</t>
+  </si>
+  <si>
     <t>FA1030</t>
   </si>
   <si>
@@ -146,6 +170,24 @@
   </si>
   <si>
     <t>FA1035</t>
+  </si>
+  <si>
+    <t>FA1036</t>
+  </si>
+  <si>
+    <t>FA1037</t>
+  </si>
+  <si>
+    <t>FA1038</t>
+  </si>
+  <si>
+    <t>FA1039</t>
+  </si>
+  <si>
+    <t>FA1040</t>
+  </si>
+  <si>
+    <t>FA1041</t>
   </si>
   <si>
     <t>TL</t>
@@ -156,10 +198,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -175,7 +225,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -183,12 +233,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -484,23 +552,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -509,152 +577,152 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="1">
-        <v>45927</v>
+        <v>16</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46079</v>
       </c>
       <c r="D2">
-        <v>257895</v>
+        <v>85546</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="1">
-        <v>45882</v>
+        <v>17</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46076</v>
       </c>
       <c r="D3">
-        <v>160526</v>
+        <v>40071</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1">
-        <v>46022</v>
+        <v>18</v>
+      </c>
+      <c r="C4" s="2">
+        <v>45894</v>
       </c>
       <c r="D4">
-        <v>129443</v>
+        <v>57653</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1">
-        <v>46037</v>
+        <v>19</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46000</v>
       </c>
       <c r="D5">
-        <v>106394</v>
+        <v>48400</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46037</v>
+        <v>20</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46054</v>
       </c>
       <c r="D6">
-        <v>17863</v>
+        <v>41007</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="1">
-        <v>46007</v>
+        <v>21</v>
+      </c>
+      <c r="C7" s="2">
+        <v>45950</v>
       </c>
       <c r="D7">
-        <v>49894</v>
+        <v>27490</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1">
-        <v>46037</v>
+        <v>22</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46093</v>
       </c>
       <c r="D8">
-        <v>101776</v>
+        <v>31218</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1">
-        <v>45947</v>
+        <v>23</v>
+      </c>
+      <c r="C9" s="2">
+        <v>45975</v>
       </c>
       <c r="D9">
-        <v>47964</v>
+        <v>62269</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1">
-        <v>45992</v>
+        <v>24</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46091</v>
       </c>
       <c r="D10">
-        <v>140963</v>
+        <v>26375</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -662,186 +730,186 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1">
-        <v>46022</v>
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>45946</v>
       </c>
       <c r="D11">
-        <v>123391</v>
+        <v>35709</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="1">
-        <v>45992</v>
+        <v>26</v>
+      </c>
+      <c r="C12" s="2">
+        <v>45879</v>
       </c>
       <c r="D12">
-        <v>37707</v>
+        <v>64911</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="1">
-        <v>45977</v>
+        <v>27</v>
+      </c>
+      <c r="C13" s="2">
+        <v>45889</v>
       </c>
       <c r="D13">
-        <v>29296</v>
+        <v>90339</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="1">
-        <v>46037</v>
+        <v>28</v>
+      </c>
+      <c r="C14" s="2">
+        <v>45991</v>
       </c>
       <c r="D14">
-        <v>69839</v>
+        <v>51862</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="1">
-        <v>45977</v>
+        <v>29</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46010</v>
       </c>
       <c r="D15">
-        <v>108483</v>
+        <v>16358</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="1">
-        <v>45917</v>
+        <v>30</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46014</v>
       </c>
       <c r="D16">
-        <v>97826</v>
+        <v>10570</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="1">
-        <v>46037</v>
+        <v>31</v>
+      </c>
+      <c r="C17" s="2">
+        <v>46073</v>
       </c>
       <c r="D17">
-        <v>100322</v>
+        <v>95587</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="1">
-        <v>45977</v>
+        <v>32</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46026</v>
       </c>
       <c r="D18">
-        <v>104319</v>
+        <v>28830</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="1">
-        <v>46037</v>
+        <v>33</v>
+      </c>
+      <c r="C19" s="2">
+        <v>45910</v>
       </c>
       <c r="D19">
-        <v>20393</v>
+        <v>78535</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="1">
-        <v>46007</v>
+        <v>34</v>
+      </c>
+      <c r="C20" s="2">
+        <v>46088</v>
       </c>
       <c r="D20">
-        <v>135221</v>
+        <v>56564</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="1">
-        <v>46037</v>
+        <v>35</v>
+      </c>
+      <c r="C21" s="2">
+        <v>46086</v>
       </c>
       <c r="D21">
-        <v>148208</v>
+        <v>54961</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -849,118 +917,373 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="1">
-        <v>45947</v>
+        <v>36</v>
+      </c>
+      <c r="C22" s="2">
+        <v>46039</v>
       </c>
       <c r="D22">
-        <v>57048</v>
+        <v>13898</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="1">
-        <v>45977</v>
+        <v>37</v>
+      </c>
+      <c r="C23" s="2">
+        <v>45926</v>
       </c>
       <c r="D23">
-        <v>38840</v>
+        <v>77258</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="1">
-        <v>45977</v>
+        <v>38</v>
+      </c>
+      <c r="C24" s="2">
+        <v>45948</v>
       </c>
       <c r="D24">
-        <v>46238</v>
+        <v>70841</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="1">
-        <v>45992</v>
+        <v>39</v>
+      </c>
+      <c r="C25" s="2">
+        <v>45973</v>
       </c>
       <c r="D25">
-        <v>123972</v>
+        <v>83470</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="1">
-        <v>46037</v>
+        <v>40</v>
+      </c>
+      <c r="C26" s="2">
+        <v>45925</v>
       </c>
       <c r="D26">
-        <v>109337</v>
+        <v>19309</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="1">
-        <v>46022</v>
+        <v>41</v>
+      </c>
+      <c r="C27" s="2">
+        <v>46033</v>
       </c>
       <c r="D27">
-        <v>97496</v>
+        <v>66975</v>
       </c>
       <c r="E27" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="2">
+        <v>45916</v>
+      </c>
+      <c r="D28">
+        <v>30811</v>
+      </c>
+      <c r="E28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="1">
-        <v>46007</v>
-      </c>
-      <c r="D28">
-        <v>38958</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="C29" s="2">
+        <v>45886</v>
+      </c>
+      <c r="D29">
+        <v>48934</v>
+      </c>
+      <c r="E29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
         <v>44</v>
+      </c>
+      <c r="C30" s="2">
+        <v>45907</v>
+      </c>
+      <c r="D30">
+        <v>97661</v>
+      </c>
+      <c r="E30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="2">
+        <v>46058</v>
+      </c>
+      <c r="D31">
+        <v>98031</v>
+      </c>
+      <c r="E31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="2">
+        <v>45943</v>
+      </c>
+      <c r="D32">
+        <v>100159</v>
+      </c>
+      <c r="E32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="2">
+        <v>46080</v>
+      </c>
+      <c r="D33">
+        <v>82172</v>
+      </c>
+      <c r="E33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="2">
+        <v>45920</v>
+      </c>
+      <c r="D34">
+        <v>101948</v>
+      </c>
+      <c r="E34" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D35">
+        <v>16963</v>
+      </c>
+      <c r="E35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="2">
+        <v>45890</v>
+      </c>
+      <c r="D36">
+        <v>68054</v>
+      </c>
+      <c r="E36" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="2">
+        <v>46012</v>
+      </c>
+      <c r="D37">
+        <v>63969</v>
+      </c>
+      <c r="E37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="D38">
+        <v>16664</v>
+      </c>
+      <c r="E38" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="2">
+        <v>46039</v>
+      </c>
+      <c r="D39">
+        <v>90357</v>
+      </c>
+      <c r="E39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="2">
+        <v>46036</v>
+      </c>
+      <c r="D40">
+        <v>39249</v>
+      </c>
+      <c r="E40" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="2">
+        <v>45989</v>
+      </c>
+      <c r="D41">
+        <v>79326</v>
+      </c>
+      <c r="E41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="2">
+        <v>46090</v>
+      </c>
+      <c r="D42">
+        <v>30429</v>
+      </c>
+      <c r="E42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D43">
+        <v>99268</v>
+      </c>
+      <c r="E43" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
